--- a/Inputs_EmpresaX_small.xlsx
+++ b/Inputs_EmpresaX_small.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kaizen\Documents\tese\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CFE5089-05DC-4B71-819D-635EDB0A152E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5876F8A7-98AE-48D2-9667-D729FCC28647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -780,7 +780,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2145" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2101" uniqueCount="536">
   <si>
     <t>ESTRUTURA FÍSICA DO SISTEMA PRODUTIVO</t>
   </si>
@@ -2360,27 +2360,15 @@
     <t>nao_produzir_segunda</t>
   </si>
   <si>
-    <t>segunda</t>
-  </si>
-  <si>
     <t>L1</t>
   </si>
   <si>
     <t>L2</t>
   </si>
   <si>
-    <t>l1</t>
-  </si>
-  <si>
     <t>tempo de produção</t>
   </si>
   <si>
-    <t>l2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pudim de Laranja </t>
-  </si>
-  <si>
     <t>unid_caixa</t>
   </si>
   <si>
@@ -2388,6 +2376,18 @@
   </si>
   <si>
     <t>Monday</t>
+  </si>
+  <si>
+    <t>dia 2 a 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 5 </t>
+  </si>
+  <si>
+    <t>4 dias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valorização </t>
   </si>
 </sst>
 </file>
@@ -2398,7 +2398,7 @@
     <numFmt numFmtId="164" formatCode="General\ &quot;min&quot;"/>
     <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2534,8 +2534,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF153E7E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2588,12 +2595,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2716,7 +2717,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2878,9 +2879,6 @@
     <xf numFmtId="14" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2890,7 +2888,6 @@
     <xf numFmtId="1" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2900,16 +2897,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2927,11 +2924,38 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3671,26 +3695,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A2E0425D-8D3D-4317-A507-ADC777C31517}" name="Table4" displayName="Table4" ref="A4:Q192" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19" tableBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A2E0425D-8D3D-4317-A507-ADC777C31517}" name="Table4" displayName="Table4" ref="A4:Q192" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
   <autoFilter ref="A4:Q192" xr:uid="{A2E0425D-8D3D-4317-A507-ADC777C31517}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{26D481BD-1A66-4F75-A5DB-835BDEAD35EC}" name="ref_id" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{AF3D888D-29CC-4818-9F37-35E1C095FEBC}" name="nome" dataDxfId="16"/>
-    <tableColumn id="21" xr3:uid="{A36D18E5-0E2F-48D2-A9EA-1667409CF7FA}" name="Unid_caixa" dataDxfId="15"/>
-    <tableColumn id="19" xr3:uid="{901BF69A-B9CB-436F-8A73-E52E627A4C44}" name="nao_produzir_segunda" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{73E06642-D2DC-4B3F-B7AE-6A99CF0B73CD}" name="família" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{47F7E5B0-45A6-4E01-8304-DD4D19A9E24E}" name="ativa" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{E576D14B-BDA0-4CA6-B2F4-097D5C1CE99B}" name="pode_L1" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{B29DBEC4-DD50-4914-98AC-30F025559FDC}" name="tempo_L1_prod_min (cadência de L1)" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{14DD02B2-C00E-494B-A8F3-3FFAE31BC4FB}" name="operadores_nec_L1_acab" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{89492EE9-DE84-43EE-B12E-2605FE3EAD79}" name="operadores_nec_L1_prod" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{780BF028-7B4E-42E1-B807-EDB2FB22CEE7}" name="pode_L2" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{FD12F15B-F3BE-48A4-B186-794E71F468D8}" name="tempo_L2_prod_min (cadência de L2)" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{2B695F9C-3774-41DD-8FE4-AF094E98B022}" name="tempo_L2_acab_min (cadência de L2)" dataDxfId="5"/>
-    <tableColumn id="20" xr3:uid="{46C45284-5F2B-442A-A3EB-D66468126784}" name="operadores_nec_L2_acab" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{1453032D-3307-46D2-BB7E-3D55B4D2E43D}" name="operadores_nec_L2_prod" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{5009F860-773A-42AE-9780-72CCCE321658}" name="kg" dataDxfId="2"/>
-    <tableColumn id="18" xr3:uid="{3939DDEA-30DE-43D1-B600-33ECEC5CD680}" name="euros" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{26D481BD-1A66-4F75-A5DB-835BDEAD35EC}" name="ref_id" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{AF3D888D-29CC-4818-9F37-35E1C095FEBC}" name="nome" dataDxfId="19"/>
+    <tableColumn id="21" xr3:uid="{A36D18E5-0E2F-48D2-A9EA-1667409CF7FA}" name="Unid_caixa" dataDxfId="18"/>
+    <tableColumn id="19" xr3:uid="{901BF69A-B9CB-436F-8A73-E52E627A4C44}" name="nao_produzir_segunda" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{73E06642-D2DC-4B3F-B7AE-6A99CF0B73CD}" name="família" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{47F7E5B0-45A6-4E01-8304-DD4D19A9E24E}" name="ativa" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{E576D14B-BDA0-4CA6-B2F4-097D5C1CE99B}" name="pode_L1" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{B29DBEC4-DD50-4914-98AC-30F025559FDC}" name="tempo_L1_prod_min (cadência de L1)" dataDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{14DD02B2-C00E-494B-A8F3-3FFAE31BC4FB}" name="operadores_nec_L1_acab" dataDxfId="12"/>
+    <tableColumn id="13" xr3:uid="{89492EE9-DE84-43EE-B12E-2605FE3EAD79}" name="operadores_nec_L1_prod" dataDxfId="11"/>
+    <tableColumn id="14" xr3:uid="{780BF028-7B4E-42E1-B807-EDB2FB22CEE7}" name="pode_L2" dataDxfId="10"/>
+    <tableColumn id="15" xr3:uid="{FD12F15B-F3BE-48A4-B186-794E71F468D8}" name="tempo_L2_prod_min (cadência de L2)" dataDxfId="9"/>
+    <tableColumn id="16" xr3:uid="{2B695F9C-3774-41DD-8FE4-AF094E98B022}" name="tempo_L2_acab_min (cadência de L2)" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{46C45284-5F2B-442A-A3EB-D66468126784}" name="operadores_nec_L2_acab" dataDxfId="7"/>
+    <tableColumn id="17" xr3:uid="{1453032D-3307-46D2-BB7E-3D55B4D2E43D}" name="operadores_nec_L2_prod" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{5009F860-773A-42AE-9780-72CCCE321658}" name="kg" dataDxfId="5"/>
+    <tableColumn id="18" xr3:uid="{3939DDEA-30DE-43D1-B600-33ECEC5CD680}" name="euros" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4029,11 +4053,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="62" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -4060,16 +4084,16 @@
         <v>469</v>
       </c>
       <c r="B5" s="31">
-        <v>46184</v>
+        <v>46182</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="69" t="s">
+      <c r="A6" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="66"/>
-      <c r="C6" s="66"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
@@ -4102,11 +4126,11 @@
       <c r="C9" s="3"/>
     </row>
     <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="69" t="s">
+      <c r="A11" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="66"/>
-      <c r="C11" s="66"/>
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
     </row>
     <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
@@ -4130,11 +4154,11 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="69" t="s">
+      <c r="A15" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="66"/>
-      <c r="C15" s="66"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="64"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
@@ -4216,11 +4240,11 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="69" t="s">
+      <c r="A24" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="66"/>
-      <c r="C24" s="66"/>
+      <c r="B24" s="64"/>
+      <c r="C24" s="64"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
@@ -4300,11 +4324,11 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="69" t="s">
+      <c r="A33" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="66"/>
-      <c r="C33" s="66"/>
+      <c r="B33" s="64"/>
+      <c r="C33" s="64"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
@@ -4319,74 +4343,69 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="73" t="s">
+      <c r="A37" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="B37" s="66"/>
-      <c r="C37" s="66"/>
+      <c r="B37" s="64"/>
+      <c r="C37" s="64"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="72" t="s">
+      <c r="A39" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="68"/>
-      <c r="C39" s="68"/>
+      <c r="B39" s="67"/>
+      <c r="C39" s="67"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="71" t="s">
+      <c r="A40" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="68"/>
-      <c r="C40" s="68"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="67"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="71"/>
-      <c r="B41" s="68"/>
-      <c r="C41" s="68"/>
+      <c r="A41" s="69"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="67"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="70" t="s">
+      <c r="A42" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="B42" s="68"/>
-      <c r="C42" s="68"/>
+      <c r="B42" s="67"/>
+      <c r="C42" s="67"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="67" t="s">
+      <c r="A43" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="68"/>
-      <c r="C43" s="68"/>
+      <c r="B43" s="67"/>
+      <c r="C43" s="67"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="71" t="s">
+      <c r="A44" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="B44" s="68"/>
-      <c r="C44" s="68"/>
+      <c r="B44" s="67"/>
+      <c r="C44" s="67"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="65"/>
-      <c r="B45" s="66"/>
-      <c r="C45" s="66"/>
+      <c r="B45" s="64"/>
+      <c r="C45" s="64"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="65"/>
-      <c r="B46" s="66"/>
-      <c r="C46" s="66"/>
+      <c r="B46" s="64"/>
+      <c r="C46" s="64"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="65"/>
-      <c r="B47" s="66"/>
-      <c r="C47" s="66"/>
+      <c r="B47" s="64"/>
+      <c r="C47" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A46:C46"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A43:C43"/>
@@ -4398,6 +4417,11 @@
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A46:C46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4429,44 +4453,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="62" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="63"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
     </row>
     <row r="2" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="74"/>
-      <c r="M2" s="74"/>
-      <c r="N2" s="74"/>
-      <c r="O2" s="74"/>
-      <c r="P2" s="74"/>
-      <c r="Q2" s="74"/>
+      <c r="B2" s="72"/>
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="72"/>
+      <c r="P2" s="72"/>
+      <c r="Q2" s="72"/>
     </row>
     <row r="4" spans="1:17" ht="31" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
@@ -12870,10 +12894,12 @@
         <v>22</v>
       </c>
       <c r="L158" s="45">
-        <v>76</v>
+        <f>76*24</f>
+        <v>1824</v>
       </c>
       <c r="M158" s="45">
-        <v>76</v>
+        <f>76*24</f>
+        <v>1824</v>
       </c>
       <c r="N158" s="45">
         <v>2</v>
@@ -14698,109 +14724,109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="63"/>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="63"/>
-      <c r="R1" s="63"/>
-      <c r="S1" s="63"/>
-      <c r="T1" s="63"/>
-      <c r="U1" s="63"/>
-      <c r="V1" s="63"/>
-      <c r="W1" s="63"/>
-      <c r="X1" s="63"/>
-      <c r="Y1" s="63"/>
-      <c r="Z1" s="63"/>
-      <c r="AA1" s="63"/>
-      <c r="AB1" s="63"/>
-      <c r="AC1" s="63"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="H1" s="61"/>
+      <c r="I1" s="61"/>
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="L1" s="61"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
+      <c r="P1" s="61"/>
+      <c r="Q1" s="61"/>
+      <c r="R1" s="61"/>
+      <c r="S1" s="61"/>
+      <c r="T1" s="61"/>
+      <c r="U1" s="61"/>
+      <c r="V1" s="61"/>
+      <c r="W1" s="61"/>
+      <c r="X1" s="61"/>
+      <c r="Y1" s="61"/>
+      <c r="Z1" s="61"/>
+      <c r="AA1" s="61"/>
+      <c r="AB1" s="61"/>
+      <c r="AC1" s="61"/>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.35">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="60" t="s">
         <v>400</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
-      <c r="J2" s="63"/>
-      <c r="K2" s="63"/>
-      <c r="L2" s="63"/>
-      <c r="M2" s="63"/>
-      <c r="N2" s="63"/>
-      <c r="O2" s="63"/>
-      <c r="P2" s="63"/>
-      <c r="Q2" s="63"/>
-      <c r="R2" s="63"/>
-      <c r="S2" s="63"/>
-      <c r="T2" s="63"/>
-      <c r="U2" s="63"/>
-      <c r="V2" s="63"/>
-      <c r="W2" s="63"/>
-      <c r="X2" s="63"/>
-      <c r="Y2" s="63"/>
-      <c r="Z2" s="63"/>
-      <c r="AA2" s="63"/>
-      <c r="AB2" s="63"/>
-      <c r="AC2" s="63"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="61"/>
+      <c r="V2" s="61"/>
+      <c r="W2" s="61"/>
+      <c r="X2" s="61"/>
+      <c r="Y2" s="61"/>
+      <c r="Z2" s="61"/>
+      <c r="AA2" s="61"/>
+      <c r="AB2" s="61"/>
+      <c r="AC2" s="61"/>
     </row>
     <row r="3" spans="1:38" ht="32" x14ac:dyDescent="0.7">
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="73" t="s">
         <v>511</v>
       </c>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
-      <c r="K3" s="75"/>
-      <c r="L3" s="75"/>
-      <c r="M3" s="75"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="W3" s="75"/>
-      <c r="X3" s="75"/>
-      <c r="Y3" s="75"/>
-      <c r="Z3" s="75"/>
-      <c r="AA3" s="75"/>
-      <c r="AB3" s="75"/>
-      <c r="AC3" s="75"/>
-      <c r="AD3" s="75"/>
-      <c r="AE3" s="75"/>
-      <c r="AF3" s="75"/>
-      <c r="AG3" s="75"/>
-      <c r="AH3" s="75"/>
-      <c r="AI3" s="75"/>
-      <c r="AJ3" s="75"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="73"/>
+      <c r="G3" s="73"/>
+      <c r="H3" s="73"/>
+      <c r="I3" s="73"/>
+      <c r="J3" s="73"/>
+      <c r="K3" s="73"/>
+      <c r="L3" s="73"/>
+      <c r="M3" s="73"/>
+      <c r="N3" s="73"/>
+      <c r="O3" s="73"/>
+      <c r="P3" s="73"/>
+      <c r="Q3" s="73"/>
+      <c r="R3" s="73"/>
+      <c r="S3" s="73"/>
+      <c r="T3" s="73"/>
+      <c r="U3" s="73"/>
+      <c r="V3" s="73"/>
+      <c r="W3" s="73"/>
+      <c r="X3" s="73"/>
+      <c r="Y3" s="73"/>
+      <c r="Z3" s="73"/>
+      <c r="AA3" s="73"/>
+      <c r="AB3" s="73"/>
+      <c r="AC3" s="73"/>
+      <c r="AD3" s="73"/>
+      <c r="AE3" s="73"/>
+      <c r="AF3" s="73"/>
+      <c r="AG3" s="73"/>
+      <c r="AH3" s="73"/>
+      <c r="AI3" s="73"/>
+      <c r="AJ3" s="73"/>
     </row>
     <row r="4" spans="1:38" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
@@ -18792,7 +18818,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="B1:N111"/>
+  <dimension ref="B1:O111"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14" style="6" customWidth="1"/>
@@ -18802,49 +18828,30 @@
     <col min="11" max="11" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B1" s="64" t="s">
+    <row r="1" spans="2:15" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="B1" s="62" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
-      <c r="I1">
-        <f>5*450/60</f>
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="2" spans="2:14" ht="35" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="62" t="s">
+    </row>
+    <row r="2" spans="2:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="60" t="s">
         <v>404</v>
       </c>
-      <c r="C2" s="63"/>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="59" t="s">
-        <v>529</v>
-      </c>
-      <c r="G2" s="59"/>
-      <c r="H2" s="58">
-        <f>SUM(F5,F8,F9,F10,F12,F14,F15,F16,F18)</f>
-        <v>36.09394871794872</v>
-      </c>
-      <c r="I2" t="s">
-        <v>531</v>
-      </c>
-      <c r="J2" s="40">
-        <f>SUM(F6,F7,F11,F13,F17,F19)</f>
-        <v>39.036189792663478</v>
-      </c>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="M3" s="61"/>
-      <c r="N3" s="61"/>
-    </row>
-    <row r="4" spans="2:14" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="57"/>
+      <c r="J2" s="40"/>
+    </row>
+    <row r="4" spans="2:15" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B4" s="35" t="s">
         <v>28</v>
       </c>
@@ -18855,1350 +18862,1359 @@
         <v>37</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="F4" s="56" t="s">
+        <v>528</v>
+      </c>
+      <c r="G4" s="56" t="s">
         <v>530</v>
       </c>
-      <c r="G4" s="56" t="s">
-        <v>534</v>
-      </c>
       <c r="H4" s="56" t="s">
+        <v>531</v>
+      </c>
+      <c r="N4" t="s">
         <v>535</v>
       </c>
-      <c r="M4" s="61"/>
-      <c r="N4" s="61"/>
-    </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B5" s="34" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C5" s="34">
         <v>168</v>
       </c>
       <c r="D5" s="37">
-        <v>46184</v>
-      </c>
-      <c r="E5" s="60">
+        <v>46182</v>
+      </c>
+      <c r="E5" s="59">
         <v>2</v>
       </c>
       <c r="F5" s="34">
-        <f>(168*2)/(_xlfn.XLOOKUP(B5,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)]))</f>
-        <v>1.8666666666666667</v>
+        <f>(C5*E5)/(_xlfn.XLOOKUP(B5,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)]))</f>
+        <v>1.5272727272727273</v>
       </c>
       <c r="G5" s="34" t="str">
         <f>_xlfn.XLOOKUP(B5,Table4[ref_id],Table4[família])</f>
-        <v>NK</v>
+        <v>AM</v>
       </c>
       <c r="H5" s="34" cm="1">
         <f t="array" ref="H5">_xlfn.XLOOKUP(B5,Table4[ref_id],'2_REFERENCIAS'!$D$5:$D$192)</f>
         <v>1</v>
       </c>
-      <c r="J5" s="55" t="s">
-        <v>48</v>
+      <c r="J5" s="55" t="str">
+        <f>_xlfn.XLOOKUP(K5,Table4[ref_id],Table4[nome])</f>
+        <v>TARTA AMERICANA RED-VELVET  PORCIONADA 1,800kg (2unid./cx)</v>
       </c>
       <c r="K5" s="55" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="L5" s="55" t="s">
-        <v>406</v>
-      </c>
-      <c r="M5" s="55" t="s">
-        <v>527</v>
-      </c>
-      <c r="N5" s="61"/>
-    </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+        <v>526</v>
+      </c>
+      <c r="N5">
+        <f>_xlfn.XLOOKUP(K5,Table4[ref_id],Table4[euros])</f>
+        <v>25.88</v>
+      </c>
+      <c r="O5">
+        <f>N5*C5</f>
+        <v>4347.84</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B6" s="34" t="s">
-        <v>232</v>
+        <v>372</v>
       </c>
       <c r="C6" s="34">
-        <v>280</v>
+        <v>576</v>
       </c>
       <c r="D6" s="37">
-        <v>46184</v>
-      </c>
-      <c r="E6" s="60">
-        <v>45</v>
+        <v>46182</v>
+      </c>
+      <c r="E6" s="59">
+        <f>_xlfn.XLOOKUP(B6,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
       </c>
       <c r="F6" s="34">
-        <f>(280*E6/800)</f>
-        <v>15.75</v>
+        <f>(C6*E6)/1824</f>
+        <v>0.63157894736842102</v>
       </c>
       <c r="G6" s="34" t="str">
         <f>_xlfn.XLOOKUP(B6,Table4[ref_id],Table4[família])</f>
-        <v>TM</v>
+        <v>BW</v>
       </c>
       <c r="H6" s="34" cm="1">
         <f t="array" ref="H6">_xlfn.XLOOKUP(B6,Table4[ref_id],'2_REFERENCIAS'!$D$5:$D$192)</f>
         <v>1</v>
       </c>
-      <c r="J6" s="55" t="s">
-        <v>56</v>
+      <c r="J6" s="55" t="str">
+        <f>_xlfn.XLOOKUP(K6,Table4[ref_id],Table4[nome])</f>
+        <v>BROWNIE C/NOZES 60 GR (48 UNID)</v>
       </c>
       <c r="K6" s="55" t="s">
-        <v>232</v>
+        <v>372</v>
       </c>
       <c r="L6" s="55" t="s">
-        <v>406</v>
-      </c>
-      <c r="M6" s="55" t="s">
-        <v>528</v>
-      </c>
-      <c r="N6" s="61"/>
-    </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+        <v>527</v>
+      </c>
+      <c r="N6">
+        <f>_xlfn.XLOOKUP(K6,Table4[ref_id],Table4[euros])</f>
+        <v>16.989999999999998</v>
+      </c>
+      <c r="O6">
+        <f>N6*C6</f>
+        <v>9786.24</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B7" s="34" t="s">
-        <v>243</v>
+        <v>521</v>
       </c>
       <c r="C7" s="34">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="D7" s="37">
-        <v>46184</v>
-      </c>
-      <c r="E7" s="60">
-        <v>90</v>
+        <v>46182</v>
+      </c>
+      <c r="E7" s="59">
+        <f>_xlfn.XLOOKUP(B7,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>4</v>
       </c>
       <c r="F7" s="34">
-        <f>(200*E7/3456)</f>
-        <v>5.208333333333333</v>
+        <f>(C7*E7)/126</f>
+        <v>4.4444444444444446</v>
       </c>
       <c r="G7" s="34" t="str">
         <f>_xlfn.XLOOKUP(B7,Table4[ref_id],Table4[família])</f>
-        <v>MF</v>
+        <v>TA</v>
       </c>
       <c r="H7" s="34" cm="1">
         <f t="array" ref="H7">_xlfn.XLOOKUP(B7,Table4[ref_id],'2_REFERENCIAS'!$D$5:$D$192)</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="55" t="s">
-        <v>66</v>
+        <v>1</v>
+      </c>
+      <c r="J7" s="55" t="str">
+        <f>_xlfn.XLOOKUP(K7,Table4[ref_id],Table4[nome])</f>
+        <v>TARTE DE AMENDOA 0,800KG(2UNID)ATRIAN</v>
       </c>
       <c r="K7" s="55" t="s">
-        <v>243</v>
+        <v>521</v>
       </c>
       <c r="L7" s="55" t="s">
-        <v>526</v>
-      </c>
-      <c r="M7" s="55" t="s">
-        <v>528</v>
-      </c>
-      <c r="N7" s="61"/>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+        <v>527</v>
+      </c>
+      <c r="N7">
+        <f>_xlfn.XLOOKUP(K7,Table4[ref_id],Table4[euros])</f>
+        <v>16.78</v>
+      </c>
+      <c r="O7">
+        <f>N7*C7</f>
+        <v>2349.2000000000003</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B8" s="34" t="s">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="C8" s="34">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="D8" s="37">
-        <v>46184</v>
-      </c>
-      <c r="E8" s="60">
-        <v>4</v>
+        <v>46178</v>
+      </c>
+      <c r="E8" s="59">
+        <f>_xlfn.XLOOKUP(B8,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>30</v>
       </c>
       <c r="F8" s="34">
-        <f>C8*E8/(_xlfn.XLOOKUP(B8,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)]))</f>
-        <v>15.384615384615385</v>
+        <f>(C8*E8)/672</f>
+        <v>6.25</v>
       </c>
       <c r="G8" s="34" t="str">
         <f>_xlfn.XLOOKUP(B8,Table4[ref_id],Table4[família])</f>
-        <v>TN</v>
+        <v>QM</v>
       </c>
       <c r="H8" s="34" cm="1">
         <f t="array" ref="H8">_xlfn.XLOOKUP(B8,Table4[ref_id],'2_REFERENCIAS'!$D$5:$D$192)</f>
         <v>1</v>
       </c>
-      <c r="J8" s="55" t="s">
-        <v>83</v>
+      <c r="J8" s="55" t="str">
+        <f>_xlfn.XLOOKUP(K8,Table4[ref_id],Table4[nome])</f>
+        <v>MINI QUEIJINHO DO CÉU (80g x 30 unidades) CX ATRIAN</v>
       </c>
       <c r="K8" s="55" t="s">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="L8" s="55" t="s">
-        <v>406</v>
-      </c>
-      <c r="M8" s="55" t="s">
         <v>527</v>
       </c>
-      <c r="N8" s="61"/>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="N8">
+        <f>_xlfn.XLOOKUP(K8,Table4[ref_id],Table4[euros])</f>
+        <v>17.11</v>
+      </c>
+      <c r="O8">
+        <f>N8*C8</f>
+        <v>2395.4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B9" s="34" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
       <c r="C9" s="34">
-        <v>96</v>
+        <v>300</v>
       </c>
       <c r="D9" s="37">
-        <v>46184</v>
-      </c>
-      <c r="E9" s="60">
-        <v>4</v>
+        <v>46182</v>
+      </c>
+      <c r="E9" s="59">
+        <f>_xlfn.XLOOKUP(B9,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>2</v>
       </c>
       <c r="F9" s="34">
-        <f>C9*E9/(_xlfn.XLOOKUP(B9,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)]))</f>
-        <v>1.92</v>
+        <f>(C9*E9)/(_xlfn.XLOOKUP(B9,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)]))</f>
+        <v>2.7272727272727271</v>
       </c>
       <c r="G9" s="34" t="str">
         <f>_xlfn.XLOOKUP(B9,Table4[ref_id],Table4[família])</f>
-        <v>TR</v>
+        <v>TL</v>
       </c>
       <c r="H9" s="34" cm="1">
         <f t="array" ref="H9">_xlfn.XLOOKUP(B9,Table4[ref_id],'2_REFERENCIAS'!$D$5:$D$192)</f>
-        <v>1</v>
-      </c>
-      <c r="J9" s="55" t="s">
-        <v>84</v>
+        <v>0</v>
+      </c>
+      <c r="J9" s="55" t="str">
+        <f>_xlfn.XLOOKUP(K9,Table4[ref_id],Table4[nome])</f>
+        <v>TORTA DE LARANJA 1,500KG(2 UNID) DOCELEIA</v>
       </c>
       <c r="K9" s="55" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L9" s="55" t="s">
-        <v>510</v>
-      </c>
-      <c r="M9" s="55" t="s">
-        <v>527</v>
-      </c>
-      <c r="N9" s="61"/>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+        <v>526</v>
+      </c>
+      <c r="N9">
+        <f>_xlfn.XLOOKUP(K9,Table4[ref_id],Table4[euros])</f>
+        <v>21</v>
+      </c>
+      <c r="O9">
+        <f>N9*C9</f>
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B10" s="34" t="s">
-        <v>298</v>
+        <v>328</v>
       </c>
       <c r="C10" s="34">
         <v>96</v>
       </c>
       <c r="D10" s="37">
-        <v>46184</v>
-      </c>
-      <c r="E10" s="60">
+        <v>46182</v>
+      </c>
+      <c r="E10" s="59">
+        <f>_xlfn.XLOOKUP(B10,Table4[ref_id],Table4[Unid_caixa])</f>
         <v>4</v>
       </c>
       <c r="F10" s="34">
-        <f>C10*E10/(_xlfn.XLOOKUP(B10,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)]))</f>
-        <v>1.92</v>
+        <f>(C10*E10)/(_xlfn.XLOOKUP(B10,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)]))</f>
+        <v>1.536</v>
       </c>
       <c r="G10" s="34" t="str">
         <f>_xlfn.XLOOKUP(B10,Table4[ref_id],Table4[família])</f>
-        <v>TR</v>
+        <v>S</v>
       </c>
       <c r="H10" s="34" cm="1">
         <f t="array" ref="H10">_xlfn.XLOOKUP(B10,Table4[ref_id],'2_REFERENCIAS'!$D$5:$D$192)</f>
         <v>1</v>
       </c>
-      <c r="J10" s="55" t="s">
-        <v>110</v>
+      <c r="J10" s="55" t="str">
+        <f>_xlfn.XLOOKUP(K10,Table4[ref_id],Table4[nome])</f>
+        <v>SEMIFRIO DE CARAMELO 1,500KG(4UNID) ULI</v>
       </c>
       <c r="K10" s="55" t="s">
-        <v>287</v>
+        <v>328</v>
       </c>
       <c r="L10" s="55" t="s">
-        <v>406</v>
-      </c>
-      <c r="M10" s="55" t="s">
-        <v>527</v>
-      </c>
-      <c r="N10" s="61"/>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+        <v>526</v>
+      </c>
+      <c r="N10">
+        <f>_xlfn.XLOOKUP(K10,Table4[ref_id],Table4[euros])</f>
+        <v>37.94</v>
+      </c>
+      <c r="O10">
+        <f>N10*C10</f>
+        <v>3642.24</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B11" s="34" t="s">
-        <v>305</v>
-      </c>
-      <c r="C11" s="34">
-        <v>192</v>
+        <v>249</v>
+      </c>
+      <c r="C11" s="76">
+        <v>96</v>
       </c>
       <c r="D11" s="37">
-        <v>46177</v>
-      </c>
-      <c r="E11" s="60">
-        <v>3</v>
+        <v>46182</v>
+      </c>
+      <c r="E11" s="59">
+        <f>_xlfn.XLOOKUP(B11,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>32</v>
       </c>
       <c r="F11" s="34">
-        <f>C11*E11/125</f>
-        <v>4.6079999999999997</v>
+        <f>(C11*E11)/(_xlfn.XLOOKUP(B11,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)]))</f>
+        <v>1.3333333333333333</v>
       </c>
       <c r="G11" s="34" t="str">
         <f>_xlfn.XLOOKUP(B11,Table4[ref_id],Table4[família])</f>
-        <v>DC</v>
+        <v>MF</v>
       </c>
       <c r="H11" s="34" cm="1">
         <f t="array" ref="H11">_xlfn.XLOOKUP(B11,Table4[ref_id],'2_REFERENCIAS'!$D$5:$D$192)</f>
-        <v>1</v>
-      </c>
-      <c r="J11" s="55" t="s">
-        <v>122</v>
+        <v>0</v>
+      </c>
+      <c r="J11" s="55" t="str">
+        <f>_xlfn.XLOOKUP(K11,Table4[ref_id],Table4[nome])</f>
+        <v>Muffin de Cacau com Avelãs 110g (32 unid)</v>
       </c>
       <c r="K11" s="55" t="s">
-        <v>298</v>
+        <v>249</v>
       </c>
       <c r="L11" s="55" t="s">
-        <v>406</v>
-      </c>
-      <c r="M11" s="55" t="s">
-        <v>527</v>
-      </c>
-      <c r="N11" s="61"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+        <v>526</v>
+      </c>
+      <c r="N11">
+        <f>_xlfn.XLOOKUP(K11,Table4[ref_id],Table4[euros])</f>
+        <v>23.11</v>
+      </c>
+      <c r="O11">
+        <f>N11*C11</f>
+        <v>2218.56</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B12" s="34" t="s">
-        <v>328</v>
+        <v>512</v>
       </c>
       <c r="C12" s="34">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D12" s="37">
-        <v>46184</v>
-      </c>
-      <c r="E12" s="60">
+        <v>46182</v>
+      </c>
+      <c r="E12" s="59">
+        <f>_xlfn.XLOOKUP(B12,Table4[ref_id],Table4[Unid_caixa])</f>
         <v>4</v>
       </c>
       <c r="F12" s="34">
-        <f>C12*E12/(_xlfn.XLOOKUP(B12,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)]))</f>
-        <v>1.536</v>
+        <f>(C12*E12)/(_xlfn.XLOOKUP(B12,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)]))</f>
+        <v>2.5846153846153848</v>
       </c>
       <c r="G12" s="34" t="str">
         <f>_xlfn.XLOOKUP(B12,Table4[ref_id],Table4[família])</f>
-        <v>S</v>
+        <v>T</v>
       </c>
       <c r="H12" s="34" cm="1">
         <f t="array" ref="H12">_xlfn.XLOOKUP(B12,Table4[ref_id],'2_REFERENCIAS'!$D$5:$D$192)</f>
-        <v>1</v>
-      </c>
-      <c r="J12" s="55" t="s">
-        <v>129</v>
+        <v>0</v>
+      </c>
+      <c r="J12" s="55" t="str">
+        <f>_xlfn.XLOOKUP(K12,Table4[ref_id],Table4[nome])</f>
+        <v>MOUSSE DE CHOCOLATE RESTAURAÇÃO 2000 ML (4UNID.)</v>
       </c>
       <c r="K12" s="55" t="s">
-        <v>305</v>
+        <v>512</v>
       </c>
       <c r="L12" s="55" t="s">
-        <v>510</v>
-      </c>
-      <c r="M12" s="55" t="s">
-        <v>528</v>
-      </c>
-      <c r="N12" s="61"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+        <v>526</v>
+      </c>
+      <c r="N12">
+        <f>_xlfn.XLOOKUP(K12,Table4[ref_id],Table4[euros])</f>
+        <v>39.58</v>
+      </c>
+      <c r="O12">
+        <f>N12*C12</f>
+        <v>3324.72</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B13" s="34" t="s">
-        <v>372</v>
+        <v>239</v>
       </c>
       <c r="C13" s="34">
-        <v>288</v>
+        <v>20</v>
       </c>
       <c r="D13" s="37">
-        <v>46184</v>
-      </c>
-      <c r="E13" s="60">
-        <v>2</v>
+        <v>46182</v>
+      </c>
+      <c r="E13" s="59">
+        <f>_xlfn.XLOOKUP(B13,Table4[ref_id],Table4[Unid_caixa])</f>
+        <v>48</v>
       </c>
       <c r="F13" s="34">
-        <f>C13*E13/76</f>
-        <v>7.5789473684210522</v>
+        <f>(C13*E13)/240</f>
+        <v>4</v>
       </c>
       <c r="G13" s="34" t="str">
         <f>_xlfn.XLOOKUP(B13,Table4[ref_id],Table4[família])</f>
-        <v>BW</v>
+        <v>X</v>
       </c>
       <c r="H13" s="34" cm="1">
         <f t="array" ref="H13">_xlfn.XLOOKUP(B13,Table4[ref_id],'2_REFERENCIAS'!$D$5:$D$192)</f>
         <v>1</v>
       </c>
-      <c r="J13" s="55" t="s">
-        <v>152</v>
+      <c r="J13" s="55" t="str">
+        <f>_xlfn.XLOOKUP(K13,Table4[ref_id],Table4[nome])</f>
+        <v>720248 -VEGAN FRUTY DE MAÇÃ 110 GR (24 UNID. X 2 CXS) ATRIAN</v>
       </c>
       <c r="K13" s="55" t="s">
-        <v>328</v>
+        <v>239</v>
       </c>
       <c r="L13" s="55" t="s">
-        <v>406</v>
-      </c>
-      <c r="M13" s="55" t="s">
         <v>527</v>
       </c>
-      <c r="N13" s="61"/>
-    </row>
-    <row r="14" spans="2:14" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="34" t="s">
-        <v>293</v>
-      </c>
-      <c r="C14" s="34">
-        <v>63</v>
-      </c>
-      <c r="D14" s="37">
-        <v>46180</v>
-      </c>
-      <c r="E14" s="60">
-        <v>4</v>
-      </c>
-      <c r="F14" s="34">
-        <f>C14*E14/(_xlfn.XLOOKUP(B14,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)]))</f>
-        <v>0.84</v>
-      </c>
-      <c r="G14" s="34" t="str">
-        <f>_xlfn.XLOOKUP(B14,Table4[ref_id],Table4[família])</f>
-        <v>BG</v>
-      </c>
-      <c r="H14" s="34" cm="1">
-        <f t="array" ref="H14">_xlfn.XLOOKUP(B14,Table4[ref_id],'2_REFERENCIAS'!$D$5:$D$192)</f>
-        <v>1</v>
-      </c>
-      <c r="J14" s="55" t="s">
-        <v>188</v>
-      </c>
-      <c r="K14" s="55" t="s">
-        <v>364</v>
-      </c>
-      <c r="L14" s="55" t="s">
-        <v>406</v>
-      </c>
-      <c r="M14" s="55" t="s">
-        <v>528</v>
-      </c>
-      <c r="N14" s="61"/>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B15" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="C15" s="34">
-        <v>63</v>
-      </c>
-      <c r="D15" s="37">
-        <v>46184</v>
-      </c>
-      <c r="E15" s="60">
-        <v>4</v>
-      </c>
-      <c r="F15" s="34">
-        <f>C15*E15/(_xlfn.XLOOKUP(B15,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)]))</f>
-        <v>0.84</v>
-      </c>
-      <c r="G15" s="34" t="str">
-        <f>_xlfn.XLOOKUP(B15,Table4[ref_id],Table4[família])</f>
-        <v>CH</v>
-      </c>
-      <c r="H15" s="34" cm="1">
-        <f t="array" ref="H15">_xlfn.XLOOKUP(B15,Table4[ref_id],'2_REFERENCIAS'!$D$5:$D$192)</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="55" t="s">
-        <v>196</v>
-      </c>
-      <c r="K15" s="55" t="s">
-        <v>372</v>
-      </c>
-      <c r="L15" s="55" t="s">
-        <v>406</v>
-      </c>
-      <c r="M15" s="55" t="s">
-        <v>528</v>
-      </c>
-      <c r="N15" s="61"/>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B16" s="34" t="s">
-        <v>514</v>
-      </c>
-      <c r="C16" s="34">
-        <v>938</v>
-      </c>
-      <c r="D16" s="37">
-        <v>46184</v>
-      </c>
-      <c r="E16" s="60">
-        <v>4</v>
-      </c>
-      <c r="F16" s="34">
-        <f>C16*E16/(_xlfn.XLOOKUP(B16,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)]))</f>
-        <v>10.72</v>
-      </c>
-      <c r="G16" s="34" t="str">
-        <f>_xlfn.XLOOKUP(B16,Table4[ref_id],Table4[família])</f>
-        <v>B</v>
-      </c>
-      <c r="H16" s="34" cm="1">
-        <f t="array" ref="H16">_xlfn.XLOOKUP(B16,Table4[ref_id],'2_REFERENCIAS'!$D$5:$D$192)</f>
-        <v>1</v>
-      </c>
-      <c r="J16" s="55" t="s">
-        <v>116</v>
-      </c>
-      <c r="K16" s="55" t="s">
-        <v>293</v>
-      </c>
-      <c r="L16" s="55" t="s">
-        <v>406</v>
-      </c>
-      <c r="M16" s="55" t="s">
+      <c r="N13">
+        <f>_xlfn.XLOOKUP(K13,Table4[ref_id],Table4[euros])</f>
+        <v>25.4</v>
+      </c>
+      <c r="O13">
+        <f>N13*C13</f>
+        <v>508</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N14" t="str">
+        <f>_xlfn.XLOOKUP(K14,Table4[ref_id],Table4[euros])</f>
+        <v/>
+      </c>
+      <c r="O14" t="e">
+        <f>N14*C15</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18" s="38"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19" s="75" t="s">
+        <v>532</v>
+      </c>
+      <c r="G19" t="s">
+        <v>534</v>
+      </c>
+      <c r="H19"/>
+      <c r="I19" s="38"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20" t="s">
+        <v>533</v>
+      </c>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20" s="38"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
+      <c r="I21" s="38"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22" s="38"/>
+      <c r="J22" s="74" t="s">
+        <v>526</v>
+      </c>
+      <c r="K22" s="14">
+        <f>SUM(F5,F9,F10,F11,F12)</f>
+        <v>9.7084941724941718</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="74" t="s">
         <v>527</v>
       </c>
-      <c r="N16" s="61"/>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B17" s="34" t="s">
-        <v>321</v>
-      </c>
-      <c r="C17" s="34">
-        <v>360</v>
-      </c>
-      <c r="D17" s="37">
-        <v>46184</v>
-      </c>
-      <c r="E17" s="60">
-        <v>3</v>
-      </c>
-      <c r="F17" s="34">
-        <f>C17*E17/220</f>
-        <v>4.9090909090909092</v>
-      </c>
-      <c r="G17" s="34" t="str">
-        <f>_xlfn.XLOOKUP(B17,Table4[ref_id],Table4[família])</f>
-        <v>X</v>
-      </c>
-      <c r="H17" s="34" cm="1">
-        <f t="array" ref="H17">_xlfn.XLOOKUP(B17,Table4[ref_id],'2_REFERENCIAS'!$D$5:$D$192)</f>
-        <v>1</v>
-      </c>
-      <c r="J17" s="55" t="s">
-        <v>157</v>
-      </c>
-      <c r="K17" s="55" t="s">
-        <v>333</v>
-      </c>
-      <c r="L17" s="55" t="s">
-        <v>526</v>
-      </c>
-      <c r="M17" s="55" t="s">
-        <v>527</v>
-      </c>
-      <c r="N17" s="61"/>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B18" s="34" t="s">
-        <v>261</v>
-      </c>
-      <c r="C18" s="34">
-        <v>64</v>
-      </c>
-      <c r="D18" s="37">
-        <v>46184</v>
-      </c>
-      <c r="E18" s="34">
-        <v>4</v>
-      </c>
-      <c r="F18" s="34">
-        <f>C18*E18/(_xlfn.XLOOKUP(B18,Table4[ref_id],Table4[tempo_L1_prod_min (cadência de L1)]))</f>
-        <v>1.0666666666666667</v>
-      </c>
-      <c r="G18" s="34" t="str">
-        <f>_xlfn.XLOOKUP(B18,Table4[ref_id],Table4[família])</f>
-        <v>B</v>
-      </c>
-      <c r="H18" s="34" cm="1">
-        <f t="array" ref="H18">_xlfn.XLOOKUP(B18,Table4[ref_id],'2_REFERENCIAS'!$D$5:$D$192)</f>
-        <v>1</v>
-      </c>
-      <c r="I18" s="38"/>
-      <c r="J18" s="55" t="s">
-        <v>516</v>
-      </c>
-      <c r="K18" s="55" t="s">
-        <v>514</v>
-      </c>
-      <c r="L18" s="55" t="s">
-        <v>406</v>
-      </c>
-      <c r="M18" s="55" t="s">
-        <v>527</v>
-      </c>
-      <c r="N18" s="61"/>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B19" s="34" t="s">
-        <v>364</v>
-      </c>
-      <c r="C19" s="34">
-        <v>72</v>
-      </c>
-      <c r="D19" s="37">
-        <v>46184</v>
-      </c>
-      <c r="E19" s="34">
-        <v>3</v>
-      </c>
-      <c r="F19" s="34">
-        <f>C19*E19/220</f>
-        <v>0.98181818181818181</v>
-      </c>
-      <c r="G19" s="34" t="str">
-        <f>_xlfn.XLOOKUP(B19,Table4[ref_id],Table4[família])</f>
-        <v>PL</v>
-      </c>
-      <c r="H19" s="34" cm="1">
-        <f t="array" ref="H19">_xlfn.XLOOKUP(B19,Table4[ref_id],'2_REFERENCIAS'!$D$5:$D$192)</f>
-        <v>1</v>
-      </c>
-      <c r="I19" s="38"/>
-      <c r="J19" s="55" t="s">
-        <v>532</v>
-      </c>
-      <c r="K19" s="55" t="s">
-        <v>321</v>
-      </c>
-      <c r="L19" s="55" t="s">
-        <v>406</v>
-      </c>
-      <c r="M19" s="55" t="s">
-        <v>528</v>
-      </c>
-      <c r="N19" s="61"/>
-    </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="38"/>
-      <c r="M20" s="61"/>
-      <c r="N20" s="61"/>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B21" s="34"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="38"/>
-      <c r="M21" s="61"/>
-      <c r="N21" s="61"/>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B22" s="34"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="38"/>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B23" s="34"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="38"/>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B24" s="34"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="57"/>
-      <c r="G24" s="57"/>
-      <c r="H24" s="57"/>
+      <c r="K23" s="14">
+        <f>SUM(F6:F8,F13)</f>
+        <v>15.326023391812866</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
       <c r="I24" s="38"/>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B25" s="34"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B25"/>
+      <c r="C25"/>
+      <c r="D25"/>
+      <c r="E25"/>
+      <c r="F25"/>
+      <c r="G25"/>
+      <c r="H25"/>
       <c r="I25" s="38"/>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="57"/>
+    <row r="26" spans="2:11" ht="23" x14ac:dyDescent="0.5">
+      <c r="B26"/>
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
       <c r="I26" s="38"/>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="57"/>
-      <c r="H27" s="57"/>
+      <c r="K26" s="77"/>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B27"/>
+      <c r="C27"/>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27"/>
       <c r="I27" s="38"/>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="57"/>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B28"/>
+      <c r="C28"/>
+      <c r="D28"/>
+      <c r="E28"/>
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28"/>
       <c r="I28" s="38"/>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B29" s="34"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="37"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B29"/>
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="E29"/>
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29"/>
       <c r="I29" s="38"/>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B30" s="34"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="37"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
       <c r="I30" s="38"/>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B31" s="34"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="37"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="57"/>
-      <c r="H31" s="57"/>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
       <c r="I31" s="38"/>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.35">
-      <c r="B32" s="34"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="57"/>
-      <c r="G32" s="57"/>
-      <c r="H32" s="57"/>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32"/>
       <c r="I32" s="38"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B33" s="34"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="57"/>
-      <c r="G33" s="57"/>
-      <c r="H33" s="57"/>
+      <c r="B33"/>
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
+      <c r="H33"/>
       <c r="I33" s="38"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B34" s="34"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="57"/>
-      <c r="G34" s="57"/>
-      <c r="H34" s="57"/>
+      <c r="B34"/>
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34"/>
       <c r="I34" s="38"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="57"/>
-      <c r="G35" s="57"/>
-      <c r="H35" s="57"/>
+      <c r="B35"/>
+      <c r="C35"/>
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35"/>
+      <c r="H35"/>
       <c r="I35" s="38"/>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="37"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
+      <c r="B36"/>
+      <c r="C36"/>
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36"/>
       <c r="I36" s="38"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B37" s="34"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="57"/>
-      <c r="H37" s="57"/>
+      <c r="B37"/>
+      <c r="C37"/>
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="G37"/>
+      <c r="H37"/>
       <c r="I37" s="38"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B38" s="34"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="57"/>
-      <c r="H38" s="57"/>
+      <c r="B38"/>
+      <c r="C38"/>
+      <c r="D38"/>
+      <c r="E38"/>
+      <c r="F38"/>
+      <c r="G38"/>
+      <c r="H38"/>
       <c r="I38" s="38"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B39" s="34"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="57"/>
-      <c r="G39" s="57"/>
-      <c r="H39" s="57"/>
+      <c r="B39"/>
+      <c r="C39"/>
+      <c r="D39"/>
+      <c r="E39"/>
+      <c r="F39"/>
+      <c r="G39"/>
+      <c r="H39"/>
       <c r="I39" s="38"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B40" s="34"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="57"/>
-      <c r="G40" s="57"/>
-      <c r="H40" s="57"/>
+      <c r="B40"/>
+      <c r="C40"/>
+      <c r="D40"/>
+      <c r="E40"/>
+      <c r="F40"/>
+      <c r="G40"/>
+      <c r="H40"/>
       <c r="I40" s="38"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B41" s="34"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="57"/>
-      <c r="G41" s="57"/>
-      <c r="H41" s="57"/>
+      <c r="B41"/>
+      <c r="C41"/>
+      <c r="D41"/>
+      <c r="E41"/>
+      <c r="F41"/>
+      <c r="G41"/>
+      <c r="H41"/>
       <c r="I41" s="38"/>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B42" s="34"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="57"/>
-      <c r="H42" s="57"/>
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
       <c r="I42" s="38"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B43" s="34"/>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="57"/>
-      <c r="G43" s="57"/>
-      <c r="H43" s="57"/>
+      <c r="B43"/>
+      <c r="C43"/>
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="F43"/>
+      <c r="G43"/>
+      <c r="H43"/>
       <c r="I43" s="38"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B44" s="34"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="37"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="57"/>
-      <c r="H44" s="57"/>
+      <c r="B44"/>
+      <c r="C44"/>
+      <c r="D44"/>
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="H44"/>
       <c r="I44" s="38"/>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B45" s="34"/>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="37"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="57"/>
-      <c r="H45" s="57"/>
+      <c r="B45"/>
+      <c r="C45"/>
+      <c r="D45"/>
+      <c r="E45"/>
+      <c r="F45"/>
+      <c r="G45"/>
+      <c r="H45"/>
       <c r="I45" s="38"/>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B46" s="34"/>
-      <c r="C46" s="34"/>
-      <c r="D46" s="34"/>
-      <c r="E46" s="37"/>
-      <c r="F46" s="57"/>
-      <c r="G46" s="57"/>
-      <c r="H46" s="57"/>
+      <c r="B46"/>
+      <c r="C46"/>
+      <c r="D46"/>
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
       <c r="I46" s="38"/>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B47" s="34"/>
-      <c r="C47" s="34"/>
-      <c r="D47" s="34"/>
-      <c r="E47" s="37"/>
-      <c r="F47" s="57"/>
-      <c r="G47" s="57"/>
-      <c r="H47" s="57"/>
+      <c r="B47"/>
+      <c r="C47"/>
+      <c r="D47"/>
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47"/>
       <c r="I47" s="38"/>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B48" s="34"/>
-      <c r="C48" s="34"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="37"/>
-      <c r="F48" s="57"/>
-      <c r="G48" s="57"/>
-      <c r="H48" s="57"/>
+      <c r="B48"/>
+      <c r="C48"/>
+      <c r="D48"/>
+      <c r="E48"/>
+      <c r="F48"/>
+      <c r="G48"/>
+      <c r="H48"/>
       <c r="I48" s="38"/>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B49" s="34"/>
-      <c r="C49" s="34"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="37"/>
-      <c r="F49" s="57"/>
-      <c r="G49" s="57"/>
-      <c r="H49" s="57"/>
+      <c r="B49"/>
+      <c r="C49"/>
+      <c r="D49"/>
+      <c r="E49"/>
+      <c r="F49"/>
+      <c r="G49"/>
+      <c r="H49"/>
       <c r="I49" s="38"/>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B50" s="34"/>
-      <c r="C50" s="34"/>
-      <c r="D50" s="34"/>
-      <c r="E50" s="37"/>
-      <c r="F50" s="57"/>
-      <c r="G50" s="57"/>
-      <c r="H50" s="57"/>
+      <c r="B50"/>
+      <c r="C50"/>
+      <c r="D50"/>
+      <c r="E50"/>
+      <c r="F50"/>
+      <c r="G50"/>
+      <c r="H50"/>
       <c r="I50" s="38"/>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B51" s="34"/>
-      <c r="C51" s="34"/>
-      <c r="D51" s="34"/>
-      <c r="E51" s="37"/>
-      <c r="F51" s="57"/>
-      <c r="G51" s="57"/>
-      <c r="H51" s="57"/>
+      <c r="B51"/>
+      <c r="C51"/>
+      <c r="D51"/>
+      <c r="E51"/>
+      <c r="F51"/>
+      <c r="G51"/>
+      <c r="H51"/>
       <c r="I51" s="38"/>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B52" s="34"/>
-      <c r="C52" s="34"/>
-      <c r="D52" s="34"/>
-      <c r="E52" s="37"/>
-      <c r="F52" s="57"/>
-      <c r="G52" s="57"/>
-      <c r="H52" s="57"/>
+      <c r="B52"/>
+      <c r="C52"/>
+      <c r="D52"/>
+      <c r="E52"/>
+      <c r="F52"/>
+      <c r="G52"/>
+      <c r="H52"/>
       <c r="I52" s="38"/>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B53" s="34"/>
-      <c r="C53" s="34"/>
-      <c r="D53" s="34"/>
-      <c r="E53" s="37"/>
-      <c r="F53" s="57"/>
-      <c r="G53" s="57"/>
-      <c r="H53" s="57"/>
+      <c r="B53"/>
+      <c r="C53"/>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="H53"/>
       <c r="I53" s="38"/>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B54" s="34"/>
-      <c r="C54" s="34"/>
-      <c r="D54" s="34"/>
-      <c r="E54" s="37"/>
-      <c r="F54" s="57"/>
-      <c r="G54" s="57"/>
-      <c r="H54" s="57"/>
+      <c r="B54"/>
+      <c r="C54"/>
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54"/>
+      <c r="G54"/>
+      <c r="H54"/>
       <c r="I54" s="38"/>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B55" s="34"/>
-      <c r="C55" s="34"/>
-      <c r="D55" s="34"/>
-      <c r="E55" s="37"/>
-      <c r="F55" s="57"/>
-      <c r="G55" s="57"/>
-      <c r="H55" s="57"/>
+      <c r="B55"/>
+      <c r="C55"/>
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="F55"/>
+      <c r="G55"/>
+      <c r="H55"/>
       <c r="I55" s="38"/>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B56" s="34"/>
-      <c r="C56" s="34"/>
-      <c r="D56" s="34"/>
-      <c r="E56" s="37"/>
-      <c r="F56" s="57"/>
-      <c r="G56" s="57"/>
-      <c r="H56" s="57"/>
+      <c r="B56"/>
+      <c r="C56"/>
+      <c r="D56"/>
+      <c r="E56"/>
+      <c r="F56"/>
+      <c r="G56"/>
+      <c r="H56"/>
       <c r="I56" s="38"/>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B57" s="34"/>
-      <c r="C57" s="34"/>
-      <c r="D57" s="34"/>
-      <c r="E57" s="37"/>
-      <c r="F57" s="57"/>
-      <c r="G57" s="57"/>
-      <c r="H57" s="57"/>
+      <c r="B57"/>
+      <c r="C57"/>
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="F57"/>
+      <c r="G57"/>
+      <c r="H57"/>
       <c r="I57" s="38"/>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B58" s="34"/>
-      <c r="C58" s="34"/>
-      <c r="D58" s="34"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="57"/>
-      <c r="G58" s="57"/>
-      <c r="H58" s="57"/>
+      <c r="B58"/>
+      <c r="C58"/>
+      <c r="D58"/>
+      <c r="E58"/>
+      <c r="F58"/>
+      <c r="G58"/>
+      <c r="H58"/>
       <c r="I58" s="38"/>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B59" s="34"/>
-      <c r="C59" s="34"/>
-      <c r="D59" s="34"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="57"/>
-      <c r="G59" s="57"/>
-      <c r="H59" s="57"/>
+      <c r="B59"/>
+      <c r="C59"/>
+      <c r="D59"/>
+      <c r="E59"/>
+      <c r="F59"/>
+      <c r="G59"/>
+      <c r="H59"/>
       <c r="I59" s="38"/>
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B60" s="34"/>
-      <c r="C60" s="34"/>
-      <c r="D60" s="34"/>
-      <c r="E60" s="37"/>
-      <c r="F60" s="57"/>
-      <c r="G60" s="57"/>
-      <c r="H60" s="57"/>
+      <c r="B60"/>
+      <c r="C60"/>
+      <c r="D60"/>
+      <c r="E60"/>
+      <c r="F60"/>
+      <c r="G60"/>
+      <c r="H60"/>
       <c r="I60" s="38"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B61" s="34"/>
-      <c r="C61" s="34"/>
-      <c r="D61" s="34"/>
-      <c r="E61" s="37"/>
-      <c r="F61" s="57"/>
-      <c r="G61" s="57"/>
-      <c r="H61" s="57"/>
+      <c r="B61"/>
+      <c r="C61"/>
+      <c r="D61"/>
+      <c r="E61"/>
+      <c r="F61"/>
+      <c r="G61"/>
+      <c r="H61"/>
       <c r="I61" s="38"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B62" s="34"/>
-      <c r="C62" s="34"/>
-      <c r="D62" s="34"/>
-      <c r="E62" s="37"/>
-      <c r="F62" s="57"/>
-      <c r="G62" s="57"/>
-      <c r="H62" s="57"/>
+      <c r="B62"/>
+      <c r="C62"/>
+      <c r="D62"/>
+      <c r="E62"/>
+      <c r="F62"/>
+      <c r="G62"/>
+      <c r="H62"/>
       <c r="I62" s="38"/>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B63" s="34"/>
-      <c r="C63" s="34"/>
-      <c r="D63" s="34"/>
-      <c r="E63" s="37"/>
-      <c r="F63" s="57"/>
-      <c r="G63" s="57"/>
-      <c r="H63" s="57"/>
+      <c r="B63"/>
+      <c r="C63"/>
+      <c r="D63"/>
+      <c r="E63"/>
+      <c r="F63"/>
+      <c r="G63"/>
+      <c r="H63"/>
       <c r="I63" s="38"/>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.35">
-      <c r="B64" s="34"/>
-      <c r="C64" s="34"/>
-      <c r="D64" s="34"/>
-      <c r="E64" s="37"/>
-      <c r="F64" s="57"/>
-      <c r="G64" s="57"/>
-      <c r="H64" s="57"/>
+      <c r="B64"/>
+      <c r="C64"/>
+      <c r="D64"/>
+      <c r="E64"/>
+      <c r="F64"/>
+      <c r="G64"/>
+      <c r="H64"/>
       <c r="I64" s="38"/>
     </row>
     <row r="65" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B65" s="34"/>
-      <c r="C65" s="34"/>
-      <c r="D65" s="34"/>
-      <c r="E65" s="37"/>
-      <c r="F65" s="57"/>
-      <c r="G65" s="57"/>
-      <c r="H65" s="57"/>
+      <c r="B65"/>
+      <c r="C65"/>
+      <c r="D65"/>
+      <c r="E65"/>
+      <c r="F65"/>
+      <c r="G65"/>
+      <c r="H65"/>
       <c r="I65" s="38"/>
     </row>
     <row r="66" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B66" s="34"/>
-      <c r="C66" s="34"/>
-      <c r="D66" s="34"/>
-      <c r="E66" s="37"/>
-      <c r="F66" s="57"/>
-      <c r="G66" s="57"/>
-      <c r="H66" s="57"/>
+      <c r="B66"/>
+      <c r="C66"/>
+      <c r="D66"/>
+      <c r="E66"/>
+      <c r="F66"/>
+      <c r="G66"/>
+      <c r="H66"/>
       <c r="I66" s="38"/>
     </row>
     <row r="67" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B67" s="34"/>
-      <c r="C67" s="34"/>
-      <c r="D67" s="34"/>
-      <c r="E67" s="37"/>
-      <c r="F67" s="57"/>
-      <c r="G67" s="57"/>
-      <c r="H67" s="57"/>
+      <c r="B67"/>
+      <c r="C67"/>
+      <c r="D67"/>
+      <c r="E67"/>
+      <c r="F67"/>
+      <c r="G67"/>
+      <c r="H67"/>
       <c r="I67" s="38"/>
     </row>
     <row r="68" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B68" s="34"/>
-      <c r="C68" s="34"/>
-      <c r="D68" s="34"/>
-      <c r="E68" s="37"/>
-      <c r="F68" s="57"/>
-      <c r="G68" s="57"/>
-      <c r="H68" s="57"/>
+      <c r="B68"/>
+      <c r="C68"/>
+      <c r="D68"/>
+      <c r="E68"/>
+      <c r="F68"/>
+      <c r="G68"/>
+      <c r="H68"/>
       <c r="I68" s="38"/>
       <c r="M68" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="69" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B69" s="34"/>
-      <c r="C69" s="34"/>
-      <c r="D69" s="34"/>
-      <c r="E69" s="37"/>
-      <c r="F69" s="57"/>
-      <c r="G69" s="57"/>
-      <c r="H69" s="57"/>
+      <c r="B69"/>
+      <c r="C69"/>
+      <c r="D69"/>
+      <c r="E69"/>
+      <c r="F69"/>
+      <c r="G69"/>
+      <c r="H69"/>
       <c r="I69" s="38"/>
     </row>
     <row r="70" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B70" s="34"/>
-      <c r="C70" s="34"/>
-      <c r="D70" s="34"/>
-      <c r="E70" s="37"/>
-      <c r="F70" s="57"/>
-      <c r="G70" s="57"/>
-      <c r="H70" s="57"/>
+      <c r="B70"/>
+      <c r="C70"/>
+      <c r="D70"/>
+      <c r="E70"/>
+      <c r="F70"/>
+      <c r="G70"/>
+      <c r="H70"/>
       <c r="I70" s="38"/>
     </row>
     <row r="71" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B71" s="34"/>
-      <c r="C71" s="34"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="37"/>
-      <c r="F71" s="57"/>
-      <c r="G71" s="57"/>
-      <c r="H71" s="57"/>
+      <c r="B71"/>
+      <c r="C71"/>
+      <c r="D71"/>
+      <c r="E71"/>
+      <c r="F71"/>
+      <c r="G71"/>
+      <c r="H71"/>
       <c r="I71" s="38"/>
     </row>
     <row r="72" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B72" s="34"/>
-      <c r="C72" s="34"/>
-      <c r="D72" s="34"/>
-      <c r="E72" s="37"/>
-      <c r="F72" s="57"/>
-      <c r="G72" s="57"/>
-      <c r="H72" s="57"/>
+      <c r="B72"/>
+      <c r="C72"/>
+      <c r="D72"/>
+      <c r="E72"/>
+      <c r="F72"/>
+      <c r="G72"/>
+      <c r="H72"/>
       <c r="I72" s="38"/>
     </row>
     <row r="73" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B73" s="34"/>
-      <c r="C73" s="34"/>
-      <c r="D73" s="34"/>
-      <c r="E73" s="37"/>
-      <c r="F73" s="57"/>
-      <c r="G73" s="57"/>
-      <c r="H73" s="57"/>
+      <c r="B73"/>
+      <c r="C73"/>
+      <c r="D73"/>
+      <c r="E73"/>
+      <c r="F73"/>
+      <c r="G73"/>
+      <c r="H73"/>
       <c r="I73" s="38"/>
     </row>
     <row r="74" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B74" s="34"/>
-      <c r="C74" s="34"/>
-      <c r="D74" s="34"/>
-      <c r="E74" s="37"/>
-      <c r="F74" s="57"/>
-      <c r="G74" s="57"/>
-      <c r="H74" s="57"/>
+      <c r="B74"/>
+      <c r="C74"/>
+      <c r="D74"/>
+      <c r="E74"/>
+      <c r="F74"/>
+      <c r="G74"/>
+      <c r="H74"/>
       <c r="I74" s="38"/>
     </row>
     <row r="75" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B75" s="34"/>
-      <c r="C75" s="34"/>
-      <c r="D75" s="34"/>
-      <c r="E75" s="37"/>
-      <c r="F75" s="57"/>
-      <c r="G75" s="57"/>
-      <c r="H75" s="57"/>
+      <c r="B75"/>
+      <c r="C75"/>
+      <c r="D75"/>
+      <c r="E75"/>
+      <c r="F75"/>
+      <c r="G75"/>
+      <c r="H75"/>
       <c r="I75" s="38"/>
     </row>
     <row r="76" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B76" s="34"/>
-      <c r="C76" s="34"/>
-      <c r="D76" s="34"/>
-      <c r="E76" s="37"/>
-      <c r="F76" s="57"/>
-      <c r="G76" s="57"/>
-      <c r="H76" s="57"/>
+      <c r="B76"/>
+      <c r="C76"/>
+      <c r="D76"/>
+      <c r="E76"/>
+      <c r="F76"/>
+      <c r="G76"/>
+      <c r="H76"/>
       <c r="I76" s="38"/>
     </row>
     <row r="77" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B77" s="34"/>
-      <c r="C77" s="34"/>
-      <c r="D77" s="34"/>
-      <c r="E77" s="37"/>
-      <c r="F77" s="57"/>
-      <c r="G77" s="57"/>
-      <c r="H77" s="57"/>
+      <c r="B77"/>
+      <c r="C77"/>
+      <c r="D77"/>
+      <c r="E77"/>
+      <c r="F77"/>
+      <c r="G77"/>
+      <c r="H77"/>
       <c r="I77" s="38"/>
     </row>
     <row r="78" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B78" s="34"/>
-      <c r="C78" s="34"/>
-      <c r="D78" s="34"/>
-      <c r="E78" s="37"/>
-      <c r="F78" s="57"/>
-      <c r="G78" s="57"/>
-      <c r="H78" s="57"/>
+      <c r="B78"/>
+      <c r="C78"/>
+      <c r="D78"/>
+      <c r="E78"/>
+      <c r="F78"/>
+      <c r="G78"/>
+      <c r="H78"/>
       <c r="I78" s="38"/>
     </row>
     <row r="79" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B79" s="34"/>
-      <c r="C79" s="34"/>
-      <c r="D79" s="34"/>
-      <c r="E79" s="37"/>
-      <c r="F79" s="57"/>
-      <c r="G79" s="57"/>
-      <c r="H79" s="57"/>
+      <c r="B79"/>
+      <c r="C79"/>
+      <c r="D79"/>
+      <c r="E79"/>
+      <c r="F79"/>
+      <c r="G79"/>
+      <c r="H79"/>
       <c r="I79" s="38"/>
     </row>
     <row r="80" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B80" s="34"/>
-      <c r="C80" s="34"/>
-      <c r="D80" s="34"/>
-      <c r="E80" s="37"/>
-      <c r="F80" s="57"/>
-      <c r="G80" s="57"/>
-      <c r="H80" s="57"/>
+      <c r="B80"/>
+      <c r="C80"/>
+      <c r="D80"/>
+      <c r="E80"/>
+      <c r="F80"/>
+      <c r="G80"/>
+      <c r="H80"/>
       <c r="I80" s="38"/>
       <c r="M80" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="81" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B81" s="34"/>
-      <c r="C81" s="34"/>
-      <c r="D81" s="34"/>
-      <c r="E81" s="37"/>
-      <c r="F81" s="57"/>
-      <c r="G81" s="57"/>
-      <c r="H81" s="57"/>
+      <c r="B81"/>
+      <c r="C81"/>
+      <c r="D81"/>
+      <c r="E81"/>
+      <c r="F81"/>
+      <c r="G81"/>
+      <c r="H81"/>
       <c r="I81" s="38"/>
     </row>
     <row r="82" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B82" s="34"/>
-      <c r="C82" s="34"/>
-      <c r="D82" s="34"/>
-      <c r="E82" s="37"/>
-      <c r="F82" s="57"/>
-      <c r="G82" s="57"/>
-      <c r="H82" s="57"/>
+      <c r="B82"/>
+      <c r="C82"/>
+      <c r="D82"/>
+      <c r="E82"/>
+      <c r="F82"/>
+      <c r="G82"/>
+      <c r="H82"/>
       <c r="I82" s="38"/>
     </row>
     <row r="83" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B83" s="34"/>
-      <c r="C83" s="34"/>
-      <c r="D83" s="34"/>
-      <c r="E83" s="37"/>
-      <c r="F83" s="57"/>
-      <c r="G83" s="57"/>
-      <c r="H83" s="57"/>
+      <c r="B83"/>
+      <c r="C83"/>
+      <c r="D83"/>
+      <c r="E83"/>
+      <c r="F83"/>
+      <c r="G83"/>
+      <c r="H83"/>
       <c r="I83" s="38"/>
     </row>
     <row r="84" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B84" s="34"/>
-      <c r="C84" s="34"/>
-      <c r="D84" s="34"/>
-      <c r="E84" s="37"/>
-      <c r="F84" s="57"/>
-      <c r="G84" s="57"/>
-      <c r="H84" s="57"/>
+      <c r="B84"/>
+      <c r="C84"/>
+      <c r="D84"/>
+      <c r="E84"/>
+      <c r="F84"/>
+      <c r="G84"/>
+      <c r="H84"/>
       <c r="I84" s="38"/>
     </row>
     <row r="85" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B85" s="34"/>
-      <c r="C85" s="34"/>
-      <c r="D85" s="34"/>
-      <c r="E85" s="37"/>
-      <c r="F85" s="57"/>
-      <c r="G85" s="57"/>
-      <c r="H85" s="57"/>
+      <c r="B85"/>
+      <c r="C85"/>
+      <c r="D85"/>
+      <c r="E85"/>
+      <c r="F85"/>
+      <c r="G85"/>
+      <c r="H85"/>
       <c r="I85" s="38"/>
     </row>
     <row r="86" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B86" s="34"/>
-      <c r="C86" s="34"/>
-      <c r="D86" s="34"/>
-      <c r="E86" s="37"/>
-      <c r="F86" s="57"/>
-      <c r="G86" s="57"/>
-      <c r="H86" s="57"/>
+      <c r="B86"/>
+      <c r="C86"/>
+      <c r="D86"/>
+      <c r="E86"/>
+      <c r="F86"/>
+      <c r="G86"/>
+      <c r="H86"/>
       <c r="I86" s="38"/>
     </row>
     <row r="87" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B87" s="34"/>
-      <c r="C87" s="34"/>
-      <c r="D87" s="34"/>
-      <c r="E87" s="37"/>
-      <c r="F87" s="57"/>
-      <c r="G87" s="57"/>
-      <c r="H87" s="57"/>
+      <c r="B87"/>
+      <c r="C87"/>
+      <c r="D87"/>
+      <c r="E87"/>
+      <c r="F87"/>
+      <c r="G87"/>
+      <c r="H87"/>
       <c r="I87" s="38"/>
       <c r="M87" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="88" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B88" s="34"/>
-      <c r="C88" s="34"/>
-      <c r="D88" s="34"/>
-      <c r="E88" s="37"/>
-      <c r="F88" s="57"/>
-      <c r="G88" s="57"/>
-      <c r="H88" s="57"/>
+      <c r="B88"/>
+      <c r="C88"/>
+      <c r="D88"/>
+      <c r="E88"/>
+      <c r="F88"/>
+      <c r="G88"/>
+      <c r="H88"/>
       <c r="I88" s="38"/>
     </row>
     <row r="89" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B89" s="34"/>
-      <c r="C89" s="34"/>
-      <c r="D89" s="34"/>
-      <c r="E89" s="37"/>
-      <c r="F89" s="57"/>
-      <c r="G89" s="57"/>
-      <c r="H89" s="57"/>
+      <c r="B89"/>
+      <c r="C89"/>
+      <c r="D89"/>
+      <c r="E89"/>
+      <c r="F89"/>
+      <c r="G89"/>
+      <c r="H89"/>
       <c r="I89" s="38"/>
     </row>
     <row r="90" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B90" s="34"/>
-      <c r="C90" s="34"/>
-      <c r="D90" s="34"/>
-      <c r="E90" s="37"/>
-      <c r="F90" s="57"/>
-      <c r="G90" s="57"/>
-      <c r="H90" s="57"/>
+      <c r="B90"/>
+      <c r="C90"/>
+      <c r="D90"/>
+      <c r="E90"/>
+      <c r="F90"/>
+      <c r="G90"/>
+      <c r="H90"/>
     </row>
     <row r="91" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B91" s="34"/>
-      <c r="C91" s="34"/>
-      <c r="D91" s="34"/>
-      <c r="E91" s="37"/>
-      <c r="F91" s="57"/>
-      <c r="G91" s="57"/>
-      <c r="H91" s="57"/>
+      <c r="B91"/>
+      <c r="C91"/>
+      <c r="D91"/>
+      <c r="E91"/>
+      <c r="F91"/>
+      <c r="G91"/>
+      <c r="H91"/>
     </row>
     <row r="92" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B92" s="34"/>
-      <c r="C92" s="34"/>
-      <c r="D92" s="34"/>
-      <c r="E92" s="37"/>
-      <c r="F92" s="57"/>
-      <c r="G92" s="57"/>
-      <c r="H92" s="57"/>
-    </row>
-    <row r="111" spans="13:13" x14ac:dyDescent="0.35">
+      <c r="B92"/>
+      <c r="C92"/>
+      <c r="D92"/>
+      <c r="E92"/>
+      <c r="F92"/>
+      <c r="G92"/>
+      <c r="H92"/>
+    </row>
+    <row r="93" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B93"/>
+      <c r="C93"/>
+      <c r="D93"/>
+      <c r="E93"/>
+      <c r="F93"/>
+      <c r="G93"/>
+      <c r="H93"/>
+    </row>
+    <row r="94" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B94"/>
+      <c r="C94"/>
+      <c r="D94"/>
+      <c r="E94"/>
+      <c r="F94"/>
+      <c r="G94"/>
+      <c r="H94"/>
+    </row>
+    <row r="95" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B95"/>
+      <c r="C95"/>
+      <c r="D95"/>
+      <c r="E95"/>
+      <c r="F95"/>
+      <c r="G95"/>
+      <c r="H95"/>
+    </row>
+    <row r="96" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B96"/>
+      <c r="C96"/>
+      <c r="D96"/>
+      <c r="E96"/>
+      <c r="F96"/>
+      <c r="G96"/>
+      <c r="H96"/>
+    </row>
+    <row r="97" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B97"/>
+      <c r="C97"/>
+      <c r="D97"/>
+      <c r="E97"/>
+      <c r="F97"/>
+      <c r="G97"/>
+      <c r="H97"/>
+    </row>
+    <row r="98" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B98"/>
+      <c r="C98"/>
+      <c r="D98"/>
+      <c r="E98"/>
+      <c r="F98"/>
+      <c r="G98"/>
+      <c r="H98"/>
+    </row>
+    <row r="99" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B99"/>
+      <c r="C99"/>
+      <c r="D99"/>
+      <c r="E99"/>
+      <c r="F99"/>
+      <c r="G99"/>
+      <c r="H99"/>
+    </row>
+    <row r="100" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B100"/>
+      <c r="C100"/>
+      <c r="D100"/>
+      <c r="E100"/>
+      <c r="F100"/>
+      <c r="G100"/>
+      <c r="H100"/>
+    </row>
+    <row r="101" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B101"/>
+      <c r="C101"/>
+      <c r="D101"/>
+      <c r="E101"/>
+      <c r="F101"/>
+      <c r="G101"/>
+      <c r="H101"/>
+    </row>
+    <row r="102" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B102"/>
+      <c r="C102"/>
+      <c r="D102"/>
+      <c r="E102"/>
+      <c r="F102"/>
+      <c r="G102"/>
+      <c r="H102"/>
+    </row>
+    <row r="103" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B103"/>
+      <c r="C103"/>
+      <c r="D103"/>
+      <c r="E103"/>
+      <c r="F103"/>
+      <c r="G103"/>
+      <c r="H103"/>
+    </row>
+    <row r="104" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B104"/>
+      <c r="C104"/>
+      <c r="D104"/>
+      <c r="E104"/>
+      <c r="F104"/>
+      <c r="G104"/>
+      <c r="H104"/>
+    </row>
+    <row r="105" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B105"/>
+      <c r="C105"/>
+      <c r="D105"/>
+      <c r="E105"/>
+      <c r="F105"/>
+      <c r="G105"/>
+      <c r="H105"/>
+    </row>
+    <row r="111" spans="2:13" x14ac:dyDescent="0.35">
       <c r="M111" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
   </sheetData>
@@ -20206,8 +20222,8 @@
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:B19">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="B5:B11">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Inputs_EmpresaX_small.xlsx
+++ b/Inputs_EmpresaX_small.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kaizen\Documents\tese\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5876F8A7-98AE-48D2-9667-D729FCC28647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F648E760-C6C0-42B9-92C0-88864E4C90EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2717,7 +2717,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2888,6 +2888,11 @@
     <xf numFmtId="1" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2897,16 +2902,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2924,38 +2929,11 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="21">
     <dxf>
       <fill>
         <patternFill>
@@ -3695,26 +3673,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A2E0425D-8D3D-4317-A507-ADC777C31517}" name="Table4" displayName="Table4" ref="A4:Q192" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{A2E0425D-8D3D-4317-A507-ADC777C31517}" name="Table4" displayName="Table4" ref="A4:Q192" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19" tableBorderDxfId="18">
   <autoFilter ref="A4:Q192" xr:uid="{A2E0425D-8D3D-4317-A507-ADC777C31517}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{26D481BD-1A66-4F75-A5DB-835BDEAD35EC}" name="ref_id" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{AF3D888D-29CC-4818-9F37-35E1C095FEBC}" name="nome" dataDxfId="19"/>
-    <tableColumn id="21" xr3:uid="{A36D18E5-0E2F-48D2-A9EA-1667409CF7FA}" name="Unid_caixa" dataDxfId="18"/>
-    <tableColumn id="19" xr3:uid="{901BF69A-B9CB-436F-8A73-E52E627A4C44}" name="nao_produzir_segunda" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{73E06642-D2DC-4B3F-B7AE-6A99CF0B73CD}" name="família" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{47F7E5B0-45A6-4E01-8304-DD4D19A9E24E}" name="ativa" dataDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{E576D14B-BDA0-4CA6-B2F4-097D5C1CE99B}" name="pode_L1" dataDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{B29DBEC4-DD50-4914-98AC-30F025559FDC}" name="tempo_L1_prod_min (cadência de L1)" dataDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{14DD02B2-C00E-494B-A8F3-3FFAE31BC4FB}" name="operadores_nec_L1_acab" dataDxfId="12"/>
-    <tableColumn id="13" xr3:uid="{89492EE9-DE84-43EE-B12E-2605FE3EAD79}" name="operadores_nec_L1_prod" dataDxfId="11"/>
-    <tableColumn id="14" xr3:uid="{780BF028-7B4E-42E1-B807-EDB2FB22CEE7}" name="pode_L2" dataDxfId="10"/>
-    <tableColumn id="15" xr3:uid="{FD12F15B-F3BE-48A4-B186-794E71F468D8}" name="tempo_L2_prod_min (cadência de L2)" dataDxfId="9"/>
-    <tableColumn id="16" xr3:uid="{2B695F9C-3774-41DD-8FE4-AF094E98B022}" name="tempo_L2_acab_min (cadência de L2)" dataDxfId="8"/>
-    <tableColumn id="20" xr3:uid="{46C45284-5F2B-442A-A3EB-D66468126784}" name="operadores_nec_L2_acab" dataDxfId="7"/>
-    <tableColumn id="17" xr3:uid="{1453032D-3307-46D2-BB7E-3D55B4D2E43D}" name="operadores_nec_L2_prod" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{5009F860-773A-42AE-9780-72CCCE321658}" name="kg" dataDxfId="5"/>
-    <tableColumn id="18" xr3:uid="{3939DDEA-30DE-43D1-B600-33ECEC5CD680}" name="euros" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{26D481BD-1A66-4F75-A5DB-835BDEAD35EC}" name="ref_id" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{AF3D888D-29CC-4818-9F37-35E1C095FEBC}" name="nome" dataDxfId="16"/>
+    <tableColumn id="21" xr3:uid="{A36D18E5-0E2F-48D2-A9EA-1667409CF7FA}" name="Unid_caixa" dataDxfId="15"/>
+    <tableColumn id="19" xr3:uid="{901BF69A-B9CB-436F-8A73-E52E627A4C44}" name="nao_produzir_segunda" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{73E06642-D2DC-4B3F-B7AE-6A99CF0B73CD}" name="família" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{47F7E5B0-45A6-4E01-8304-DD4D19A9E24E}" name="ativa" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{E576D14B-BDA0-4CA6-B2F4-097D5C1CE99B}" name="pode_L1" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{B29DBEC4-DD50-4914-98AC-30F025559FDC}" name="tempo_L1_prod_min (cadência de L1)" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{14DD02B2-C00E-494B-A8F3-3FFAE31BC4FB}" name="operadores_nec_L1_acab" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{89492EE9-DE84-43EE-B12E-2605FE3EAD79}" name="operadores_nec_L1_prod" dataDxfId="8"/>
+    <tableColumn id="14" xr3:uid="{780BF028-7B4E-42E1-B807-EDB2FB22CEE7}" name="pode_L2" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{FD12F15B-F3BE-48A4-B186-794E71F468D8}" name="tempo_L2_prod_min (cadência de L2)" dataDxfId="6"/>
+    <tableColumn id="16" xr3:uid="{2B695F9C-3774-41DD-8FE4-AF094E98B022}" name="tempo_L2_acab_min (cadência de L2)" dataDxfId="5"/>
+    <tableColumn id="20" xr3:uid="{46C45284-5F2B-442A-A3EB-D66468126784}" name="operadores_nec_L2_acab" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{1453032D-3307-46D2-BB7E-3D55B4D2E43D}" name="operadores_nec_L2_prod" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{5009F860-773A-42AE-9780-72CCCE321658}" name="kg" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{3939DDEA-30DE-43D1-B600-33ECEC5CD680}" name="euros" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4053,11 +4031,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -4089,11 +4067,11 @@
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="63" t="s">
+      <c r="A6" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="67"/>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
@@ -4126,11 +4104,11 @@
       <c r="C9" s="3"/>
     </row>
     <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="63" t="s">
+      <c r="A11" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
     </row>
     <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
@@ -4154,11 +4132,11 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="63" t="s">
+      <c r="A15" s="70" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="64"/>
+      <c r="B15" s="67"/>
+      <c r="C15" s="67"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
@@ -4240,11 +4218,11 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="63" t="s">
+      <c r="A24" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="64"/>
-      <c r="C24" s="64"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="67"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
@@ -4324,11 +4302,11 @@
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="63" t="s">
+      <c r="A33" s="70" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="64"/>
-      <c r="C33" s="64"/>
+      <c r="B33" s="67"/>
+      <c r="C33" s="67"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="12" t="s">
@@ -4343,69 +4321,74 @@
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="71" t="s">
+      <c r="A37" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="B37" s="64"/>
-      <c r="C37" s="64"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="67"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="70" t="s">
+      <c r="A39" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="67"/>
-      <c r="C39" s="67"/>
+      <c r="B39" s="69"/>
+      <c r="C39" s="69"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="69" t="s">
+      <c r="A40" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="67"/>
-      <c r="C40" s="67"/>
+      <c r="B40" s="69"/>
+      <c r="C40" s="69"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="69"/>
-      <c r="B41" s="67"/>
-      <c r="C41" s="67"/>
+      <c r="A41" s="72"/>
+      <c r="B41" s="69"/>
+      <c r="C41" s="69"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="68" t="s">
+      <c r="A42" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="B42" s="67"/>
-      <c r="C42" s="67"/>
+      <c r="B42" s="69"/>
+      <c r="C42" s="69"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="66" t="s">
+      <c r="A43" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="67"/>
-      <c r="C43" s="67"/>
+      <c r="B43" s="69"/>
+      <c r="C43" s="69"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="69" t="s">
+      <c r="A44" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="B44" s="67"/>
-      <c r="C44" s="67"/>
+      <c r="B44" s="69"/>
+      <c r="C44" s="69"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="65"/>
-      <c r="B45" s="64"/>
-      <c r="C45" s="64"/>
+      <c r="A45" s="66"/>
+      <c r="B45" s="67"/>
+      <c r="C45" s="67"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="65"/>
-      <c r="B46" s="64"/>
-      <c r="C46" s="64"/>
+      <c r="A46" s="66"/>
+      <c r="B46" s="67"/>
+      <c r="C46" s="67"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="65"/>
-      <c r="B47" s="64"/>
-      <c r="C47" s="64"/>
+      <c r="A47" s="66"/>
+      <c r="B47" s="67"/>
+      <c r="C47" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A46:C46"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A43:C43"/>
@@ -4417,11 +4400,6 @@
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A46:C46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4453,44 +4431,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
     </row>
     <row r="2" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="72"/>
-      <c r="P2" s="72"/>
-      <c r="Q2" s="72"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="75"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="75"/>
+      <c r="O2" s="75"/>
+      <c r="P2" s="75"/>
+      <c r="Q2" s="75"/>
     </row>
     <row r="4" spans="1:17" ht="31" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
@@ -14724,109 +14702,109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
-      <c r="S1" s="61"/>
-      <c r="T1" s="61"/>
-      <c r="U1" s="61"/>
-      <c r="V1" s="61"/>
-      <c r="W1" s="61"/>
-      <c r="X1" s="61"/>
-      <c r="Y1" s="61"/>
-      <c r="Z1" s="61"/>
-      <c r="AA1" s="61"/>
-      <c r="AB1" s="61"/>
-      <c r="AC1" s="61"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+      <c r="N1" s="64"/>
+      <c r="O1" s="64"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="64"/>
+      <c r="U1" s="64"/>
+      <c r="V1" s="64"/>
+      <c r="W1" s="64"/>
+      <c r="X1" s="64"/>
+      <c r="Y1" s="64"/>
+      <c r="Z1" s="64"/>
+      <c r="AA1" s="64"/>
+      <c r="AB1" s="64"/>
+      <c r="AC1" s="64"/>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.35">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="63" t="s">
         <v>400</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="61"/>
-      <c r="V2" s="61"/>
-      <c r="W2" s="61"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
-      <c r="AC2" s="61"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="64"/>
+      <c r="K2" s="64"/>
+      <c r="L2" s="64"/>
+      <c r="M2" s="64"/>
+      <c r="N2" s="64"/>
+      <c r="O2" s="64"/>
+      <c r="P2" s="64"/>
+      <c r="Q2" s="64"/>
+      <c r="R2" s="64"/>
+      <c r="S2" s="64"/>
+      <c r="T2" s="64"/>
+      <c r="U2" s="64"/>
+      <c r="V2" s="64"/>
+      <c r="W2" s="64"/>
+      <c r="X2" s="64"/>
+      <c r="Y2" s="64"/>
+      <c r="Z2" s="64"/>
+      <c r="AA2" s="64"/>
+      <c r="AB2" s="64"/>
+      <c r="AC2" s="64"/>
     </row>
     <row r="3" spans="1:38" ht="32" x14ac:dyDescent="0.7">
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="76" t="s">
         <v>511</v>
       </c>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73"/>
-      <c r="K3" s="73"/>
-      <c r="L3" s="73"/>
-      <c r="M3" s="73"/>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73"/>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
-      <c r="V3" s="73"/>
-      <c r="W3" s="73"/>
-      <c r="X3" s="73"/>
-      <c r="Y3" s="73"/>
-      <c r="Z3" s="73"/>
-      <c r="AA3" s="73"/>
-      <c r="AB3" s="73"/>
-      <c r="AC3" s="73"/>
-      <c r="AD3" s="73"/>
-      <c r="AE3" s="73"/>
-      <c r="AF3" s="73"/>
-      <c r="AG3" s="73"/>
-      <c r="AH3" s="73"/>
-      <c r="AI3" s="73"/>
-      <c r="AJ3" s="73"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="76"/>
+      <c r="K3" s="76"/>
+      <c r="L3" s="76"/>
+      <c r="M3" s="76"/>
+      <c r="N3" s="76"/>
+      <c r="O3" s="76"/>
+      <c r="P3" s="76"/>
+      <c r="Q3" s="76"/>
+      <c r="R3" s="76"/>
+      <c r="S3" s="76"/>
+      <c r="T3" s="76"/>
+      <c r="U3" s="76"/>
+      <c r="V3" s="76"/>
+      <c r="W3" s="76"/>
+      <c r="X3" s="76"/>
+      <c r="Y3" s="76"/>
+      <c r="Z3" s="76"/>
+      <c r="AA3" s="76"/>
+      <c r="AB3" s="76"/>
+      <c r="AC3" s="76"/>
+      <c r="AD3" s="76"/>
+      <c r="AE3" s="76"/>
+      <c r="AF3" s="76"/>
+      <c r="AG3" s="76"/>
+      <c r="AH3" s="76"/>
+      <c r="AI3" s="76"/>
+      <c r="AJ3" s="76"/>
     </row>
     <row r="4" spans="1:38" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
@@ -18829,23 +18807,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:15" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
     </row>
     <row r="2" spans="2:15" ht="35" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="63" t="s">
         <v>404</v>
       </c>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
       <c r="F2" s="58"/>
       <c r="G2" s="58"/>
       <c r="H2" s="57"/>
@@ -18917,7 +18895,7 @@
         <v>25.88</v>
       </c>
       <c r="O5">
-        <f>N5*C5</f>
+        <f t="shared" ref="O5:O13" si="0">N5*C5</f>
         <v>4347.84</v>
       </c>
     </row>
@@ -18962,7 +18940,7 @@
         <v>16.989999999999998</v>
       </c>
       <c r="O6">
-        <f>N6*C6</f>
+        <f t="shared" si="0"/>
         <v>9786.24</v>
       </c>
     </row>
@@ -19007,7 +18985,7 @@
         <v>16.78</v>
       </c>
       <c r="O7">
-        <f>N7*C7</f>
+        <f t="shared" si="0"/>
         <v>2349.2000000000003</v>
       </c>
     </row>
@@ -19052,7 +19030,7 @@
         <v>17.11</v>
       </c>
       <c r="O8">
-        <f>N8*C8</f>
+        <f t="shared" si="0"/>
         <v>2395.4</v>
       </c>
     </row>
@@ -19097,7 +19075,7 @@
         <v>21</v>
       </c>
       <c r="O9">
-        <f>N9*C9</f>
+        <f t="shared" si="0"/>
         <v>6300</v>
       </c>
     </row>
@@ -19142,7 +19120,7 @@
         <v>37.94</v>
       </c>
       <c r="O10">
-        <f>N10*C10</f>
+        <f t="shared" si="0"/>
         <v>3642.24</v>
       </c>
     </row>
@@ -19150,7 +19128,7 @@
       <c r="B11" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="C11" s="76">
+      <c r="C11" s="61">
         <v>96</v>
       </c>
       <c r="D11" s="37">
@@ -19187,7 +19165,7 @@
         <v>23.11</v>
       </c>
       <c r="O11">
-        <f>N11*C11</f>
+        <f t="shared" si="0"/>
         <v>2218.56</v>
       </c>
     </row>
@@ -19232,7 +19210,7 @@
         <v>39.58</v>
       </c>
       <c r="O12">
-        <f>N12*C12</f>
+        <f t="shared" si="0"/>
         <v>3324.72</v>
       </c>
     </row>
@@ -19277,7 +19255,7 @@
         <v>25.4</v>
       </c>
       <c r="O13">
-        <f>N13*C13</f>
+        <f t="shared" si="0"/>
         <v>508</v>
       </c>
     </row>
@@ -19333,7 +19311,7 @@
       <c r="C19"/>
       <c r="D19"/>
       <c r="E19"/>
-      <c r="F19" s="75" t="s">
+      <c r="F19" s="60" t="s">
         <v>532</v>
       </c>
       <c r="G19" t="s">
@@ -19373,7 +19351,7 @@
       <c r="G22"/>
       <c r="H22"/>
       <c r="I22" s="38"/>
-      <c r="J22" s="74" t="s">
+      <c r="J22" s="55" t="s">
         <v>526</v>
       </c>
       <c r="K22" s="14">
@@ -19390,7 +19368,7 @@
       <c r="G23"/>
       <c r="H23"/>
       <c r="I23" s="38"/>
-      <c r="J23" s="74" t="s">
+      <c r="J23" s="55" t="s">
         <v>527</v>
       </c>
       <c r="K23" s="14">
@@ -19427,7 +19405,7 @@
       <c r="G26"/>
       <c r="H26"/>
       <c r="I26" s="38"/>
-      <c r="K26" s="77"/>
+      <c r="K26" s="62"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B27"/>
@@ -20223,7 +20201,7 @@
     <mergeCell ref="B1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B11">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
